--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/12.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/12.xlsx
@@ -426,13 +426,13 @@
         <v>-8.507597747286596</v>
       </c>
       <c r="E2">
-        <v>-10.92837820351015</v>
+        <v>-20.72928657120099</v>
       </c>
       <c r="F2">
-        <v>-1.85308122159728</v>
+        <v>-2.212795624425952</v>
       </c>
       <c r="G2">
-        <v>-12.57318164408608</v>
+        <v>-15.23176820812644</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.439792203575013</v>
       </c>
       <c r="E3">
-        <v>-11.34088142934285</v>
+        <v>-21.47874449099643</v>
       </c>
       <c r="F3">
-        <v>-1.889685120392185</v>
+        <v>-2.113818973669856</v>
       </c>
       <c r="G3">
-        <v>-12.64293483859853</v>
+        <v>-15.26471310206049</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.216501418212747</v>
       </c>
       <c r="E4">
-        <v>-12.20308023803325</v>
+        <v>-21.5837009330722</v>
       </c>
       <c r="F4">
-        <v>-1.653486095892739</v>
+        <v>-2.2864292028608</v>
       </c>
       <c r="G4">
-        <v>-12.16877533264533</v>
+        <v>-14.82083019033671</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.84237300209924</v>
       </c>
       <c r="E5">
-        <v>-13.53017218835109</v>
+        <v>-21.26487824903618</v>
       </c>
       <c r="F5">
-        <v>-0.9825805675891833</v>
+        <v>-1.903914815637475</v>
       </c>
       <c r="G5">
-        <v>-13.78627477767784</v>
+        <v>-14.37231085958517</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.331071156627583</v>
       </c>
       <c r="E6">
-        <v>-13.48473348015812</v>
+        <v>-22.00211381748491</v>
       </c>
       <c r="F6">
-        <v>-1.373146685967719</v>
+        <v>-1.830091541067385</v>
       </c>
       <c r="G6">
-        <v>-12.75284495050233</v>
+        <v>-14.76993551848872</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.709263892341458</v>
       </c>
       <c r="E7">
-        <v>-13.87503812640522</v>
+        <v>-22.41063198619087</v>
       </c>
       <c r="F7">
-        <v>-0.9193363731202466</v>
+        <v>-1.957850645601153</v>
       </c>
       <c r="G7">
-        <v>-11.94227773848501</v>
+        <v>-14.18856730579177</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.005447055947829</v>
       </c>
       <c r="E8">
-        <v>-14.69783468275488</v>
+        <v>-22.24391168712447</v>
       </c>
       <c r="F8">
-        <v>-0.8141237725558759</v>
+        <v>-1.758030203963051</v>
       </c>
       <c r="G8">
-        <v>-11.93781512309808</v>
+        <v>-14.55942785928308</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.245279398495239</v>
       </c>
       <c r="E9">
-        <v>-14.75702636650914</v>
+        <v>-23.6806878063821</v>
       </c>
       <c r="F9">
-        <v>-0.584359506041377</v>
+        <v>-1.623781669195752</v>
       </c>
       <c r="G9">
-        <v>-11.50577237749549</v>
+        <v>-14.51400386393874</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.456615437477343</v>
       </c>
       <c r="E10">
-        <v>-15.72185398163537</v>
+        <v>-23.14683506256585</v>
       </c>
       <c r="F10">
-        <v>-0.1562451500287449</v>
+        <v>-1.543184834372971</v>
       </c>
       <c r="G10">
-        <v>-10.73511048140855</v>
+        <v>-13.72522831793368</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.670949192851523</v>
       </c>
       <c r="E11">
-        <v>-16.42971333919635</v>
+        <v>-24.4463033214369</v>
       </c>
       <c r="F11">
-        <v>-0.1398393336163007</v>
+        <v>-1.469440254706148</v>
       </c>
       <c r="G11">
-        <v>-10.65395245751332</v>
+        <v>-13.47017395795161</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.910589239909496</v>
       </c>
       <c r="E12">
-        <v>-18.39518879884949</v>
+        <v>-24.95647214619303</v>
       </c>
       <c r="F12">
-        <v>-0.07360473282325783</v>
+        <v>-1.418588436583092</v>
       </c>
       <c r="G12">
-        <v>-10.22674641894361</v>
+        <v>-13.09849238916656</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.190075409072321</v>
       </c>
       <c r="E13">
-        <v>-17.80350744195529</v>
+        <v>-26.53942740641824</v>
       </c>
       <c r="F13">
-        <v>-0.3144898317203401</v>
+        <v>-1.307669212980835</v>
       </c>
       <c r="G13">
-        <v>-10.23357607439112</v>
+        <v>-12.1896119062695</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.529469678856971</v>
       </c>
       <c r="E14">
-        <v>-18.42773494154261</v>
+        <v>-26.3428010650052</v>
       </c>
       <c r="F14">
-        <v>0.1555821616114898</v>
+        <v>-1.360379887555774</v>
       </c>
       <c r="G14">
-        <v>-8.757182011878971</v>
+        <v>-12.82245910210212</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.9353415880016788</v>
       </c>
       <c r="E15">
-        <v>-20.11481340462619</v>
+        <v>-26.98675006889592</v>
       </c>
       <c r="F15">
-        <v>0.3248093383294008</v>
+        <v>-0.841234580914698</v>
       </c>
       <c r="G15">
-        <v>-8.705338868733984</v>
+        <v>-11.44554693304507</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.4073059226320465</v>
       </c>
       <c r="E16">
-        <v>-20.33871021651343</v>
+        <v>-28.05842702823314</v>
       </c>
       <c r="F16">
-        <v>0.6413243811020779</v>
+        <v>-0.9979757757702121</v>
       </c>
       <c r="G16">
-        <v>-8.84030649982453</v>
+        <v>-11.53796412231936</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.05273600545501442</v>
       </c>
       <c r="E17">
-        <v>-20.92858924075257</v>
+        <v>-29.38681865059117</v>
       </c>
       <c r="F17">
-        <v>0.9125384957178584</v>
+        <v>-0.7729257481450452</v>
       </c>
       <c r="G17">
-        <v>-7.066297703877437</v>
+        <v>-11.30017756787013</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.4488402622864661</v>
       </c>
       <c r="E18">
-        <v>-21.04012102708749</v>
+        <v>-28.79512370827496</v>
       </c>
       <c r="F18">
-        <v>0.7597047099013496</v>
+        <v>-0.6608443250766609</v>
       </c>
       <c r="G18">
-        <v>-6.734928648124087</v>
+        <v>-10.5681927753185</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.787178550110468</v>
       </c>
       <c r="E19">
-        <v>-22.38740997147953</v>
+        <v>-30.26569356481482</v>
       </c>
       <c r="F19">
-        <v>1.130564796134688</v>
+        <v>-0.6247854920327984</v>
       </c>
       <c r="G19">
-        <v>-7.024392818441342</v>
+        <v>-9.638919331899537</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.07071457604651</v>
       </c>
       <c r="E20">
-        <v>-23.45708534530536</v>
+        <v>-30.81434309745113</v>
       </c>
       <c r="F20">
-        <v>1.177667423392674</v>
+        <v>-0.01886124464184969</v>
       </c>
       <c r="G20">
-        <v>-6.277262280047542</v>
+        <v>-9.945465917199432</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.300438792319644</v>
       </c>
       <c r="E21">
-        <v>-24.26640063453418</v>
+        <v>-31.06145739557569</v>
       </c>
       <c r="F21">
-        <v>1.270770949262921</v>
+        <v>0.1234241106674102</v>
       </c>
       <c r="G21">
-        <v>-5.936064214588096</v>
+        <v>-10.04096853491633</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.478298149747458</v>
       </c>
       <c r="E22">
-        <v>-24.68516673991949</v>
+        <v>-31.38395720050594</v>
       </c>
       <c r="F22">
-        <v>1.568431521580479</v>
+        <v>-0.2145680137576497</v>
       </c>
       <c r="G22">
-        <v>-5.562075195562169</v>
+        <v>-9.29940302357404</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.605582424432106</v>
       </c>
       <c r="E23">
-        <v>-25.07692049784904</v>
+        <v>-32.06849038845341</v>
       </c>
       <c r="F23">
-        <v>1.775296399611988</v>
+        <v>-0.003026173369934346</v>
       </c>
       <c r="G23">
-        <v>-5.776893185059937</v>
+        <v>-9.359366934926859</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.682556845082727</v>
       </c>
       <c r="E24">
-        <v>-25.88024008749171</v>
+        <v>-33.02214625820272</v>
       </c>
       <c r="F24">
-        <v>1.800657696016098</v>
+        <v>0.09919353576812184</v>
       </c>
       <c r="G24">
-        <v>-5.39963996813229</v>
+        <v>-9.100243914477025</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.712486180322203</v>
       </c>
       <c r="E25">
-        <v>-26.04259946608872</v>
+        <v>-32.92140129695407</v>
       </c>
       <c r="F25">
-        <v>1.632136288325372</v>
+        <v>0.1719614702670444</v>
       </c>
       <c r="G25">
-        <v>-5.029415039384514</v>
+        <v>-9.562508630307619</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.699311789814519</v>
       </c>
       <c r="E26">
-        <v>-26.59515027908263</v>
+        <v>-32.07884700850895</v>
       </c>
       <c r="F26">
-        <v>1.768975956328628</v>
+        <v>0.5099593932639239</v>
       </c>
       <c r="G26">
-        <v>-5.205999538449239</v>
+        <v>-8.535481398205057</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.645562065172104</v>
       </c>
       <c r="E27">
-        <v>-26.26768726663997</v>
+        <v>-33.21607136487019</v>
       </c>
       <c r="F27">
-        <v>1.717915389620067</v>
+        <v>0.4185995807765692</v>
       </c>
       <c r="G27">
-        <v>-5.111410631301183</v>
+        <v>-8.994432257950839</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.553938462554856</v>
       </c>
       <c r="E28">
-        <v>-26.69046559999607</v>
+        <v>-33.00310176076346</v>
       </c>
       <c r="F28">
-        <v>2.237083062181017</v>
+        <v>0.06767912629601745</v>
       </c>
       <c r="G28">
-        <v>-5.190274447137701</v>
+        <v>-9.505027628109254</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.427054072385283</v>
       </c>
       <c r="E29">
-        <v>-26.10291873987088</v>
+        <v>-32.76057254257166</v>
       </c>
       <c r="F29">
-        <v>1.868434716913153</v>
+        <v>0.04713727144139532</v>
       </c>
       <c r="G29">
-        <v>-5.315072082331607</v>
+        <v>-9.751501054053533</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.265374623601131</v>
       </c>
       <c r="E30">
-        <v>-25.87353341748635</v>
+        <v>-33.21695441730169</v>
       </c>
       <c r="F30">
-        <v>1.895676407321618</v>
+        <v>0.354308329910494</v>
       </c>
       <c r="G30">
-        <v>-5.877414589814368</v>
+        <v>-9.151669928884065</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.068180477534574</v>
       </c>
       <c r="E31">
-        <v>-26.04916122492583</v>
+        <v>-32.95375497950187</v>
       </c>
       <c r="F31">
-        <v>1.925273974623644</v>
+        <v>0.783079581273546</v>
       </c>
       <c r="G31">
-        <v>-5.241445549538216</v>
+        <v>-9.080400504514634</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.8355952604702007</v>
       </c>
       <c r="E32">
-        <v>-25.55017773096865</v>
+        <v>-32.60053174266658</v>
       </c>
       <c r="F32">
-        <v>1.857258383914583</v>
+        <v>0.1266116684333827</v>
       </c>
       <c r="G32">
-        <v>-5.697956537221556</v>
+        <v>-9.503124064424172</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.5645077948645123</v>
       </c>
       <c r="E33">
-        <v>-25.42504240871469</v>
+        <v>-31.43875626447276</v>
       </c>
       <c r="F33">
-        <v>1.822226726450191</v>
+        <v>0.1480721827377095</v>
       </c>
       <c r="G33">
-        <v>-5.613590594698769</v>
+        <v>-9.545518910600078</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.2517858948415271</v>
       </c>
       <c r="E34">
-        <v>-25.67982341333424</v>
+        <v>-31.53038314330696</v>
       </c>
       <c r="F34">
-        <v>1.916808059767033</v>
+        <v>0.4537231870226711</v>
       </c>
       <c r="G34">
-        <v>-6.190539229100794</v>
+        <v>-10.23062968886117</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.1031332151989661</v>
       </c>
       <c r="E35">
-        <v>-25.98879666640358</v>
+        <v>-31.67439540946189</v>
       </c>
       <c r="F35">
-        <v>1.851045628393586</v>
+        <v>0.5041674483835498</v>
       </c>
       <c r="G35">
-        <v>-5.996706787776466</v>
+        <v>-9.925096130496295</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.5016895976697389</v>
       </c>
       <c r="E36">
-        <v>-24.47471496736102</v>
+        <v>-31.24846752243345</v>
       </c>
       <c r="F36">
-        <v>1.77803995245006</v>
+        <v>0.1006539474992574</v>
       </c>
       <c r="G36">
-        <v>-6.172308054816027</v>
+        <v>-10.15703957206871</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.9457268149727682</v>
       </c>
       <c r="E37">
-        <v>-24.2706664570494</v>
+        <v>-31.26400924522777</v>
       </c>
       <c r="F37">
-        <v>2.301939259615802</v>
+        <v>0.5355932225435546</v>
       </c>
       <c r="G37">
-        <v>-6.755271950462909</v>
+        <v>-10.05741201460989</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.433864627306524</v>
       </c>
       <c r="E38">
-        <v>-23.25876535461344</v>
+        <v>-30.11665695674838</v>
       </c>
       <c r="F38">
-        <v>1.990791209245863</v>
+        <v>0.3745718533177755</v>
       </c>
       <c r="G38">
-        <v>-7.165720007512829</v>
+        <v>-10.05755105752254</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.961502544098318</v>
       </c>
       <c r="E39">
-        <v>-22.64654283962046</v>
+        <v>-30.2859335793921</v>
       </c>
       <c r="F39">
-        <v>2.015088881904778</v>
+        <v>0.7047209951731297</v>
       </c>
       <c r="G39">
-        <v>-7.018039881551481</v>
+        <v>-10.1041403648967</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.526770204090382</v>
       </c>
       <c r="E40">
-        <v>-22.45602540964375</v>
+        <v>-29.41958668851068</v>
       </c>
       <c r="F40">
-        <v>1.913701682006535</v>
+        <v>0.09584610309340905</v>
       </c>
       <c r="G40">
-        <v>-6.753020779496204</v>
+        <v>-9.653181162082717</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.124059407258015</v>
       </c>
       <c r="E41">
-        <v>-22.58039994826442</v>
+        <v>-29.37834134724882</v>
       </c>
       <c r="F41">
-        <v>2.431716267142789</v>
+        <v>0.3144771117142826</v>
       </c>
       <c r="G41">
-        <v>-7.238965827569204</v>
+        <v>-9.556768144342522</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.739128765826192</v>
       </c>
       <c r="E42">
-        <v>-20.24256618485658</v>
+        <v>-29.27152823082989</v>
       </c>
       <c r="F42">
-        <v>2.230901784621328</v>
+        <v>0.5075761802460698</v>
       </c>
       <c r="G42">
-        <v>-7.091471092158055</v>
+        <v>-9.391015750282293</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.366379085749474</v>
       </c>
       <c r="E43">
-        <v>-20.24424624871343</v>
+        <v>-26.7905494040396</v>
       </c>
       <c r="F43">
-        <v>2.327774382174313</v>
+        <v>0.7612139953092504</v>
       </c>
       <c r="G43">
-        <v>-7.671041678627183</v>
+        <v>-10.48238674548613</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.997831680520043</v>
       </c>
       <c r="E44">
-        <v>-18.73216613518226</v>
+        <v>-26.63119240370968</v>
       </c>
       <c r="F44">
-        <v>1.826250935292991</v>
+        <v>0.3810546566120844</v>
       </c>
       <c r="G44">
-        <v>-8.073653674385648</v>
+        <v>-10.34365171357189</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.618428175117055</v>
       </c>
       <c r="E45">
-        <v>-19.0878958823808</v>
+        <v>-26.80696965079141</v>
       </c>
       <c r="F45">
-        <v>2.206068986620204</v>
+        <v>0.4467259675712236</v>
       </c>
       <c r="G45">
-        <v>-7.090511033951666</v>
+        <v>-9.951563942082768</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.223131066351588</v>
       </c>
       <c r="E46">
-        <v>-18.88221259295241</v>
+        <v>-26.11765892276585</v>
       </c>
       <c r="F46">
-        <v>2.001261773217249</v>
+        <v>0.5194806481917014</v>
       </c>
       <c r="G46">
-        <v>-8.320282695970272</v>
+        <v>-10.30013790300371</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.806741947206564</v>
       </c>
       <c r="E47">
-        <v>-18.3435958944801</v>
+        <v>-25.33893347545884</v>
       </c>
       <c r="F47">
-        <v>2.188785929128195</v>
+        <v>0.5182389254549049</v>
       </c>
       <c r="G47">
-        <v>-7.651698161041221</v>
+        <v>-10.20554237476457</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.357411782054305</v>
       </c>
       <c r="E48">
-        <v>-17.5590332441772</v>
+        <v>-24.77281082586394</v>
       </c>
       <c r="F48">
-        <v>1.91476530575173</v>
+        <v>0.4235267100884207</v>
       </c>
       <c r="G48">
-        <v>-7.768192948022635</v>
+        <v>-10.87869546253782</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.866034684060399</v>
       </c>
       <c r="E49">
-        <v>-16.64464830102241</v>
+        <v>-25.29178753256499</v>
       </c>
       <c r="F49">
-        <v>1.829592569395885</v>
+        <v>0.5126209377291187</v>
       </c>
       <c r="G49">
-        <v>-8.435976330931183</v>
+        <v>-10.12975405573404</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.330067643100792</v>
       </c>
       <c r="E50">
-        <v>-16.37402216585002</v>
+        <v>-24.4201513840426</v>
       </c>
       <c r="F50">
-        <v>1.821784378257097</v>
+        <v>0.4298405264325585</v>
       </c>
       <c r="G50">
-        <v>-8.44153142634608</v>
+        <v>-10.69886993939015</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.74106142639844</v>
       </c>
       <c r="E51">
-        <v>-16.37740040745974</v>
+        <v>-23.39155379794036</v>
       </c>
       <c r="F51">
-        <v>1.92318648876859</v>
+        <v>0.2040839014128036</v>
       </c>
       <c r="G51">
-        <v>-8.151626953472103</v>
+        <v>-10.32506300036888</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.086913225087244</v>
       </c>
       <c r="E52">
-        <v>-14.65233710439982</v>
+        <v>-23.08960873653092</v>
       </c>
       <c r="F52">
-        <v>1.897318231513967</v>
+        <v>0.220902244791842</v>
       </c>
       <c r="G52">
-        <v>-8.239846371002601</v>
+        <v>-10.74112243210787</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.368656838223293</v>
       </c>
       <c r="E53">
-        <v>-15.03246626955168</v>
+        <v>-22.50171318390714</v>
       </c>
       <c r="F53">
-        <v>1.440765194195825</v>
+        <v>0.08918437244009542</v>
       </c>
       <c r="G53">
-        <v>-8.040412486625826</v>
+        <v>-10.98892007626786</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.581193690641339</v>
       </c>
       <c r="E54">
-        <v>-13.66687323322063</v>
+        <v>-23.24954991000783</v>
       </c>
       <c r="F54">
-        <v>1.796225930411121</v>
+        <v>0.4405952204231045</v>
       </c>
       <c r="G54">
-        <v>-9.029580319941282</v>
+        <v>-11.1057459178032</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.711659483697929</v>
       </c>
       <c r="E55">
-        <v>-12.8135094773192</v>
+        <v>-21.42378693043934</v>
       </c>
       <c r="F55">
-        <v>1.713303039921279</v>
+        <v>0.2658941919074944</v>
       </c>
       <c r="G55">
-        <v>-8.661636357070064</v>
+        <v>-11.89552290383389</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.762601469734827</v>
       </c>
       <c r="E56">
-        <v>-12.24877254077064</v>
+        <v>-22.59749946611738</v>
       </c>
       <c r="F56">
-        <v>1.636041212262169</v>
+        <v>0.2801238871527842</v>
       </c>
       <c r="G56">
-        <v>-8.565792753162624</v>
+        <v>-11.34376752098572</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.733581185780086</v>
       </c>
       <c r="E57">
-        <v>-12.85691942915673</v>
+        <v>-21.51561079789287</v>
       </c>
       <c r="F57">
-        <v>1.608481428771029</v>
+        <v>0.1441747141075378</v>
       </c>
       <c r="G57">
-        <v>-8.34513827187912</v>
+        <v>-11.52755907768944</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.617790090316594</v>
       </c>
       <c r="E58">
-        <v>-11.94132085496788</v>
+        <v>-20.97439022686615</v>
       </c>
       <c r="F58">
-        <v>1.514075709343581</v>
+        <v>-0.09265718308764645</v>
       </c>
       <c r="G58">
-        <v>-8.917574632711119</v>
+        <v>-11.60234099087603</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.418066877957591</v>
       </c>
       <c r="E59">
-        <v>-11.20780769215345</v>
+        <v>-20.66261384838606</v>
       </c>
       <c r="F59">
-        <v>1.518832194970456</v>
+        <v>0.4362785978871163</v>
       </c>
       <c r="G59">
-        <v>-7.977492258106438</v>
+        <v>-11.20966725282646</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.140014914044954</v>
       </c>
       <c r="E60">
-        <v>-11.89465493031884</v>
+        <v>-19.96430051403325</v>
       </c>
       <c r="F60">
-        <v>1.179968628037651</v>
+        <v>-0.235869481520639</v>
       </c>
       <c r="G60">
-        <v>-9.208869534711592</v>
+        <v>-11.99708713043319</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.782875135466943</v>
       </c>
       <c r="E61">
-        <v>-11.36843266520552</v>
+        <v>-19.43069230781343</v>
       </c>
       <c r="F61">
-        <v>0.8573410621997162</v>
+        <v>-0.07124305735787644</v>
       </c>
       <c r="G61">
-        <v>-8.848337883302802</v>
+        <v>-11.64593756508269</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.34700587623489</v>
       </c>
       <c r="E62">
-        <v>-10.02256566165188</v>
+        <v>-19.37386448749117</v>
       </c>
       <c r="F62">
-        <v>0.6088838568736437</v>
+        <v>0.02002894818478149</v>
       </c>
       <c r="G62">
-        <v>-8.432033471193911</v>
+        <v>-11.14713435813517</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.84338154244883</v>
       </c>
       <c r="E63">
-        <v>-10.7365882723373</v>
+        <v>-18.58256346786486</v>
       </c>
       <c r="F63">
-        <v>0.4851655285307319</v>
+        <v>-0.2599468084504094</v>
       </c>
       <c r="G63">
-        <v>-8.579091214593877</v>
+        <v>-11.09418549278006</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.275390381206155</v>
       </c>
       <c r="E64">
-        <v>-9.524727871618643</v>
+        <v>-19.9067662517658</v>
       </c>
       <c r="F64">
-        <v>0.6445003417244112</v>
+        <v>0.1382841935062305</v>
       </c>
       <c r="G64">
-        <v>-8.010309696037233</v>
+        <v>-11.34736939453244</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.644126257083734</v>
       </c>
       <c r="E65">
-        <v>-8.259091842058899</v>
+        <v>-19.89275968166008</v>
       </c>
       <c r="F65">
-        <v>0.7336790628401948</v>
+        <v>-0.1780602055814699</v>
       </c>
       <c r="G65">
-        <v>-7.878573157393015</v>
+        <v>-10.74572740095299</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.963611818893734</v>
       </c>
       <c r="E66">
-        <v>-10.70550935522266</v>
+        <v>-18.77250578164259</v>
       </c>
       <c r="F66">
-        <v>0.5617638339001993</v>
+        <v>-0.4975507440650028</v>
       </c>
       <c r="G66">
-        <v>-7.58502046333476</v>
+        <v>-11.30058476497146</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.24076149492385</v>
       </c>
       <c r="E67">
-        <v>-10.33653835002569</v>
+        <v>-18.51832253559205</v>
       </c>
       <c r="F67">
-        <v>0.480215204931602</v>
+        <v>-0.2837035571952964</v>
       </c>
       <c r="G67">
-        <v>-7.83421846825786</v>
+        <v>-11.51667400395631</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.481168355894784</v>
       </c>
       <c r="E68">
-        <v>-8.511567853408545</v>
+        <v>-19.13244248119425</v>
       </c>
       <c r="F68">
-        <v>0.1574782945964979</v>
+        <v>-0.8224322976059549</v>
       </c>
       <c r="G68">
-        <v>-7.206155010729487</v>
+        <v>-10.8661584265806</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.695328905535698</v>
       </c>
       <c r="E69">
-        <v>-9.090424571913017</v>
+        <v>-18.77742823288892</v>
       </c>
       <c r="F69">
-        <v>0.1860718806063312</v>
+        <v>-0.4395144954574666</v>
       </c>
       <c r="G69">
-        <v>-8.207363298171272</v>
+        <v>-11.25706102276667</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.890920574358949</v>
       </c>
       <c r="E70">
-        <v>-10.17381669350807</v>
+        <v>-18.86324734380828</v>
       </c>
       <c r="F70">
-        <v>0.3557215246996699</v>
+        <v>-0.9663031481241731</v>
       </c>
       <c r="G70">
-        <v>-7.285793494222195</v>
+        <v>-10.80831988546399</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.073637495463862</v>
       </c>
       <c r="E71">
-        <v>-9.087657674294329</v>
+        <v>-18.82960983887931</v>
       </c>
       <c r="F71">
-        <v>0.3283613777526051</v>
+        <v>-0.9297870562739652</v>
       </c>
       <c r="G71">
-        <v>-7.027054497054916</v>
+        <v>-10.58546720194242</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.247913501695037</v>
       </c>
       <c r="E72">
-        <v>-8.679587824515139</v>
+        <v>-18.01907186166842</v>
       </c>
       <c r="F72">
-        <v>0.09585024493042305</v>
+        <v>-1.01786239200922</v>
       </c>
       <c r="G72">
-        <v>-7.136911640230091</v>
+        <v>-10.86675763532321</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.4193467198341405</v>
       </c>
       <c r="E73">
-        <v>-9.54527808666545</v>
+        <v>-19.00505197888447</v>
       </c>
       <c r="F73">
-        <v>-0.1132081499836994</v>
+        <v>-1.027895577991927</v>
       </c>
       <c r="G73">
-        <v>-7.038704306807611</v>
+        <v>-10.45370748947942</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.4091796529149326</v>
       </c>
       <c r="E74">
-        <v>-8.726122423417959</v>
+        <v>-19.51133537294202</v>
       </c>
       <c r="F74">
-        <v>0.02305083247019409</v>
+        <v>-0.9718697770709858</v>
       </c>
       <c r="G74">
-        <v>-5.748180823597838</v>
+        <v>-10.42386292144289</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>1.236296328535463</v>
       </c>
       <c r="E75">
-        <v>-9.978000948942398</v>
+        <v>-18.68309106236114</v>
       </c>
       <c r="F75">
-        <v>-0.3479368223431757</v>
+        <v>-1.201186725187973</v>
       </c>
       <c r="G75">
-        <v>-6.375919847663362</v>
+        <v>-9.910288060299136</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>2.057514221474135</v>
       </c>
       <c r="E76">
-        <v>-9.815093624990466</v>
+        <v>-19.11125827978637</v>
       </c>
       <c r="F76">
-        <v>-0.2696196546128992</v>
+        <v>-1.439860911486983</v>
       </c>
       <c r="G76">
-        <v>-6.108510531728732</v>
+        <v>-9.856812818203288</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>2.869611732950624</v>
       </c>
       <c r="E77">
-        <v>-10.056289207587</v>
+        <v>-18.93663579357659</v>
       </c>
       <c r="F77">
-        <v>-0.1765426364995412</v>
+        <v>-1.299827887145935</v>
       </c>
       <c r="G77">
-        <v>-5.61358397360769</v>
+        <v>-10.30138928921756</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>3.665405065318282</v>
       </c>
       <c r="E78">
-        <v>-10.56403982722303</v>
+        <v>-19.6762171115613</v>
       </c>
       <c r="F78">
-        <v>-0.6128743971479443</v>
+        <v>-0.9830825582352798</v>
       </c>
       <c r="G78">
-        <v>-5.313701516478349</v>
+        <v>-9.309179064551509</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>4.43860870428603</v>
       </c>
       <c r="E79">
-        <v>-11.41633939173266</v>
+        <v>-19.45772729763922</v>
       </c>
       <c r="F79">
-        <v>-0.7916907549206624</v>
+        <v>-1.588806340714751</v>
       </c>
       <c r="G79">
-        <v>-4.571556659666691</v>
+        <v>-9.379044817612288</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>5.181889401706774</v>
       </c>
       <c r="E80">
-        <v>-11.88990456108479</v>
+        <v>-21.15027162885006</v>
       </c>
       <c r="F80">
-        <v>-0.4186885105836843</v>
+        <v>-1.301857387282794</v>
       </c>
       <c r="G80">
-        <v>-4.71142389815536</v>
+        <v>-9.455472071931903</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>5.879638339454583</v>
       </c>
       <c r="E81">
-        <v>-12.12347419345241</v>
+        <v>-21.4125472579523</v>
       </c>
       <c r="F81">
-        <v>-0.2084463786509614</v>
+        <v>-1.188240171049619</v>
       </c>
       <c r="G81">
-        <v>-4.202977072051933</v>
+        <v>-9.150488064126545</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>6.525028352813946</v>
       </c>
       <c r="E82">
-        <v>-13.14269783835878</v>
+        <v>-21.05171844902113</v>
       </c>
       <c r="F82">
-        <v>-0.611710540947011</v>
+        <v>-1.479355812517658</v>
       </c>
       <c r="G82">
-        <v>-4.296917112274293</v>
+        <v>-8.919882082951991</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>7.108333398031583</v>
       </c>
       <c r="E83">
-        <v>-13.34443682692649</v>
+        <v>-23.06090726827031</v>
       </c>
       <c r="F83">
-        <v>-0.4845246666559806</v>
+        <v>-1.295833499529636</v>
       </c>
       <c r="G83">
-        <v>-3.544562533019523</v>
+        <v>-9.300634546514649</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>7.61489485466193</v>
       </c>
       <c r="E84">
-        <v>-14.65643990185077</v>
+        <v>-23.31912991313569</v>
       </c>
       <c r="F84">
-        <v>-0.2443047467833463</v>
+        <v>-1.3680812192996</v>
       </c>
       <c r="G84">
-        <v>-3.286826631150643</v>
+        <v>-9.21618915089892</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>8.036636169483439</v>
       </c>
       <c r="E85">
-        <v>-15.67144300898199</v>
+        <v>-24.06474768697262</v>
       </c>
       <c r="F85">
-        <v>-0.564920208199881</v>
+        <v>-1.211098969529872</v>
       </c>
       <c r="G85">
-        <v>-3.681350964156669</v>
+        <v>-8.9222093964661</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>8.368483372404157</v>
       </c>
       <c r="E86">
-        <v>-17.62232772538241</v>
+        <v>-24.90945752904539</v>
       </c>
       <c r="F86">
-        <v>-0.7232700925516317</v>
+        <v>-1.726489286734057</v>
       </c>
       <c r="G86">
-        <v>-3.151921900425342</v>
+        <v>-8.744856850836264</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>8.602226150231933</v>
       </c>
       <c r="E87">
-        <v>-18.10008173319163</v>
+        <v>-25.00215539198241</v>
       </c>
       <c r="F87">
-        <v>-0.3141493727177895</v>
+        <v>-1.750160713636456</v>
       </c>
       <c r="G87">
-        <v>-3.262735791261366</v>
+        <v>-9.004731365123513</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>8.731229656213488</v>
       </c>
       <c r="E88">
-        <v>-19.8556986503813</v>
+        <v>-26.59714733612001</v>
       </c>
       <c r="F88">
-        <v>-0.3397939707736566</v>
+        <v>-1.660474203302756</v>
       </c>
       <c r="G88">
-        <v>-3.162442814149146</v>
+        <v>-8.960485923991152</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>8.759047056606949</v>
       </c>
       <c r="E89">
-        <v>-20.40601239721543</v>
+        <v>-28.48409905648014</v>
       </c>
       <c r="F89">
-        <v>-0.7109166494736827</v>
+        <v>-1.389989052001439</v>
       </c>
       <c r="G89">
-        <v>-3.239333544844258</v>
+        <v>-8.672349282435146</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>8.686456166541092</v>
       </c>
       <c r="E90">
-        <v>-22.92386658785018</v>
+        <v>-30.11739056953762</v>
       </c>
       <c r="F90">
-        <v>-0.3677348032700839</v>
+        <v>-1.758757510542709</v>
       </c>
       <c r="G90">
-        <v>-3.618347971998799</v>
+        <v>-9.19979201884291</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>8.512347158514563</v>
       </c>
       <c r="E91">
-        <v>-24.25647874798337</v>
+        <v>-30.53583515326839</v>
       </c>
       <c r="F91">
-        <v>-0.3461193842614336</v>
+        <v>-1.838390125708631</v>
       </c>
       <c r="G91">
-        <v>-3.61411709479961</v>
+        <v>-8.348908983248352</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>8.250018631856094</v>
       </c>
       <c r="E92">
-        <v>-26.48301167723069</v>
+        <v>-32.44619229153716</v>
       </c>
       <c r="F92">
-        <v>-0.6430890981650563</v>
+        <v>-1.977269234257579</v>
       </c>
       <c r="G92">
-        <v>-3.184885002359865</v>
+        <v>-8.860610075616881</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>7.909890276968634</v>
       </c>
       <c r="E93">
-        <v>-27.6260664438768</v>
+        <v>-34.01538778349008</v>
       </c>
       <c r="F93">
-        <v>-0.1152459337945862</v>
+        <v>-1.481258572441889</v>
       </c>
       <c r="G93">
-        <v>-3.467198394312294</v>
+        <v>-9.192611445568231</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>7.497743676572667</v>
       </c>
       <c r="E94">
-        <v>-30.69493176634287</v>
+        <v>-35.56338548861308</v>
       </c>
       <c r="F94">
-        <v>-0.1102980952976647</v>
+        <v>-1.821997563174631</v>
       </c>
       <c r="G94">
-        <v>-3.904428764774918</v>
+        <v>-8.275477772641777</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>7.03319405571793</v>
       </c>
       <c r="E95">
-        <v>-31.93501361707732</v>
+        <v>-36.72435942690755</v>
       </c>
       <c r="F95">
-        <v>-0.0974368630017996</v>
+        <v>-1.699789348607023</v>
       </c>
       <c r="G95">
-        <v>-4.199517551963395</v>
+        <v>-9.276950903726704</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>6.528588612608059</v>
       </c>
       <c r="E96">
-        <v>-33.80389219767284</v>
+        <v>-39.12715641419242</v>
       </c>
       <c r="F96">
-        <v>-0.09188514466823731</v>
+        <v>-2.136600733981648</v>
       </c>
       <c r="G96">
-        <v>-3.834463695347961</v>
+        <v>-9.034605728069895</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>5.999763092524539</v>
       </c>
       <c r="E97">
-        <v>-35.9297322431226</v>
+        <v>-40.40200109564676</v>
       </c>
       <c r="F97">
-        <v>-0.03183182143488435</v>
+        <v>-1.682716696435326</v>
       </c>
       <c r="G97">
-        <v>-4.385090182167241</v>
+        <v>-9.372340962895263</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>5.444362043480412</v>
       </c>
       <c r="E98">
-        <v>-39.02254413614123</v>
+        <v>-42.38789997307449</v>
       </c>
       <c r="F98">
-        <v>-0.01821677480247168</v>
+        <v>-1.657714911484031</v>
       </c>
       <c r="G98">
-        <v>-5.114274253192653</v>
+        <v>-9.629672978208353</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>4.897373502959936</v>
       </c>
       <c r="E99">
-        <v>-40.43756093779199</v>
+        <v>-44.50801149890454</v>
       </c>
       <c r="F99">
-        <v>0.2596714959776645</v>
+        <v>-1.994243310708344</v>
       </c>
       <c r="G99">
-        <v>-5.393449247973853</v>
+        <v>-10.0696279276498</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>4.32861657565466</v>
       </c>
       <c r="E100">
-        <v>-42.34916793488689</v>
+        <v>-46.28961506418724</v>
       </c>
       <c r="F100">
-        <v>0.2921211322475295</v>
+        <v>-2.065345398360237</v>
       </c>
       <c r="G100">
-        <v>-5.250817703959893</v>
+        <v>-10.17679690784708</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>3.787798017503463</v>
       </c>
       <c r="E101">
-        <v>-44.60856852848187</v>
+        <v>-48.03442477815761</v>
       </c>
       <c r="F101">
-        <v>0.2533957845340554</v>
+        <v>-2.118630131545315</v>
       </c>
       <c r="G101">
-        <v>-5.165216927950957</v>
+        <v>-10.59510088946169</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>3.196260276349806</v>
       </c>
       <c r="E102">
-        <v>-46.47667047578507</v>
+        <v>-49.45558105844427</v>
       </c>
       <c r="F102">
-        <v>0.1093965370684034</v>
+        <v>-1.946509467489425</v>
       </c>
       <c r="G102">
-        <v>-6.103064684316632</v>
+        <v>-10.06929025200479</v>
       </c>
     </row>
   </sheetData>
